--- a/Design Files/LED Board - v1.0/BOM/JLCPCB-BOM-LED Board-v1.0.xlsx
+++ b/Design Files/LED Board - v1.0/BOM/JLCPCB-BOM-LED Board-v1.0.xlsx
@@ -27,9 +27,6 @@
     <t>100nF</t>
   </si>
   <si>
-    <t>SM04B-SRSS-TB(LF)(SN)</t>
-  </si>
-  <si>
     <t>WS2812B-XF02/W</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
     <t>C106256</t>
   </si>
   <si>
-    <t>C160404</t>
-  </si>
-  <si>
     <t>C4154882</t>
   </si>
   <si>
@@ -85,6 +79,12 @@
   </si>
   <si>
     <t>C128539</t>
+  </si>
+  <si>
+    <t>ZX-SH1.0-4PWT</t>
+  </si>
+  <si>
+    <t>C7430446</t>
   </si>
 </sst>
 </file>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -558,69 +558,69 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>2</v>
+      <c r="A3" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
